--- a/ComcastCRMGUIFramework/testData/TestData1.xlsx
+++ b/ComcastCRMGUIFramework/testData/TestData1.xlsx
@@ -1,9 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{ADAA3C4B-6B72-490D-8060-5C78FDBF83D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Guru K R\git\CRM_LOCAL_GIT_REPO\ComcastCRMGUIFramework\testData\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC824AB-53D0-4384-B2C0-98430BDDEBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="1" xr2:uid="{C583224A-11DF-45A6-93F1-F6C972DB6544}"/>
   </bookViews>
@@ -18,7 +23,6 @@
     <sheet name="ECommerce" sheetId="4" r:id="rId8"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1:L26"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
